--- a/architectures and decision enablers/architecture decision enabler/cloud-security-posturing/Cloud_Security_Assessment.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/cloud-security-posturing/Cloud_Security_Assessment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\cloud-security-posturing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amit\eBooks\Interview Quick Rampup\Fractional Architect Consulting &amp; Freelancing\UPWORK &amp; TOPMATE FILES AND PRODUCTS\CLOUD_SECURITY_ASSESSMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1663712B-AB23-48AC-9AFB-AA0E39E14C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F3A31D-43C0-4506-AF29-E6F927A087C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="124">
   <si>
     <t>Category</t>
   </si>
@@ -1912,12 +1912,15 @@
   <si>
     <t>☠️ State 4: Critical Cloud Threat Posture (Score: 81% – 100%)</t>
   </si>
+  <si>
+    <t>© 2026 Amit Kulkarni All rights reserved.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1995,6 +1998,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2038,7 +2049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2075,12 +2086,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2091,6 +2097,29 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2098,72 +2127,7 @@
   <dxfs count="11">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFDCDFE5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2212,6 +2176,73 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFDCDFE5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3600,7 +3631,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B54C481-2366-4FC4-84A3-2AB441592D85}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6B54C481-2366-4FC4-84A3-2AB441592D85}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B23:D40" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -3732,13 +3763,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D90B28C5-67E5-426D-8A4B-D0120A7E64AD}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D90B28C5-67E5-426D-8A4B-D0120A7E64AD}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9">
   <autoFilter ref="A1:D76" xr:uid="{D90B28C5-67E5-426D-8A4B-D0120A7E64AD}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8431A441-4ECE-4A90-A222-02A773BE052E}" name="Category" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{95B0C528-7571-4ECB-9F08-6EFA807C316D}" name="Client-Specific Question" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{28F77A17-2EC1-4471-B442-2EE24E12C641}" name="User Priority" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{F1E6196C-5F62-481B-B30A-58A8AEDCBC71}" name="User Score" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{8431A441-4ECE-4A90-A222-02A773BE052E}" name="Category" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{95B0C528-7571-4ECB-9F08-6EFA807C316D}" name="Client-Specific Question" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{28F77A17-2EC1-4471-B442-2EE24E12C641}" name="User Priority" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{F1E6196C-5F62-481B-B30A-58A8AEDCBC71}" name="User Score" dataDxfId="6">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3760,12 +3791,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5F2DA1A1-3406-4AF6-98DD-0ED725F042BA}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5F2DA1A1-3406-4AF6-98DD-0ED725F042BA}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:C5" xr:uid="{5F2DA1A1-3406-4AF6-98DD-0ED725F042BA}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F014942C-3959-42B4-BE32-78D0A70F5CF7}" name="States"/>
-    <tableColumn id="2" xr3:uid="{79FFC482-DD0D-4E1E-85E6-B2A80E0413F4}" name="Definitions" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{E69330B5-6666-488B-9EDC-D0D797F513EB}" name="Operational Impact" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{79FFC482-DD0D-4E1E-85E6-B2A80E0413F4}" name="Definitions" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{E69330B5-6666-488B-9EDC-D0D797F513EB}" name="Operational Impact" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4099,12 +4130,12 @@
       <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" cm="1">
+      <c r="C2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="21" cm="1">
         <f t="array" ref="D2">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="93.6" x14ac:dyDescent="0.35">
@@ -4114,12 +4145,12 @@
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2" cm="1">
+      <c r="C3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="21" cm="1">
         <f t="array" ref="D3">_xlfn.SWITCH(C3,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="100.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -4129,12 +4160,12 @@
       <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" cm="1">
+      <c r="C4" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="21" cm="1">
         <f t="array" ref="D4">_xlfn.SWITCH(C4,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="93.6" x14ac:dyDescent="0.35">
@@ -4144,10 +4175,10 @@
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" cm="1">
+      <c r="D5" s="21" cm="1">
         <f t="array" ref="D5">_xlfn.SWITCH(C5,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4159,10 +4190,10 @@
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" cm="1">
+      <c r="D6" s="21" cm="1">
         <f t="array" ref="D6">_xlfn.SWITCH(C6,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4174,12 +4205,12 @@
       <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" cm="1">
+      <c r="C7" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="21" cm="1">
         <f t="array" ref="D7">_xlfn.SWITCH(C7,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="109.2" x14ac:dyDescent="0.3">
@@ -4189,12 +4220,12 @@
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2" cm="1">
+      <c r="C8" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="21" cm="1">
         <f t="array" ref="D8">_xlfn.SWITCH(C8,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="109.2" x14ac:dyDescent="0.3">
@@ -4204,27 +4235,27 @@
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="2" cm="1">
+      <c r="C9" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="21" cm="1">
         <f t="array" ref="D9">_xlfn.SWITCH(C9,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="2" cm="1">
+      <c r="C10" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="21" cm="1">
         <f t="array" ref="D10">_xlfn.SWITCH(C10,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
@@ -4234,12 +4265,12 @@
       <c r="B11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" cm="1">
+      <c r="C11" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="21" cm="1">
         <f t="array" ref="D11">_xlfn.SWITCH(C11,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4249,10 +4280,10 @@
       <c r="B12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2" cm="1">
+      <c r="D12" s="21" cm="1">
         <f t="array" ref="D12">_xlfn.SWITCH(C12,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4264,10 +4295,10 @@
       <c r="B13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2" cm="1">
+      <c r="D13" s="21" cm="1">
         <f t="array" ref="D13">_xlfn.SWITCH(C13,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4279,12 +4310,12 @@
       <c r="B14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="2" cm="1">
+      <c r="C14" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="21" cm="1">
         <f t="array" ref="D14">_xlfn.SWITCH(C14,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4294,8 +4325,10 @@
       <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="21"/>
     </row>
     <row r="16" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -4304,12 +4337,12 @@
       <c r="B16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="2" cm="1">
+      <c r="C16" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="21" cm="1">
         <f t="array" ref="D16">_xlfn.SWITCH(C16,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4319,12 +4352,12 @@
       <c r="B17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="2" cm="1">
+      <c r="C17" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="21" cm="1">
         <f t="array" ref="D17">_xlfn.SWITCH(C17,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4334,12 +4367,12 @@
       <c r="B18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="2" cm="1">
+      <c r="C18" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="21" cm="1">
         <f t="array" ref="D18">_xlfn.SWITCH(C18,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4349,12 +4382,12 @@
       <c r="B19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" cm="1">
+      <c r="C19" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="21" cm="1">
         <f t="array" ref="D19">_xlfn.SWITCH(C19,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4364,10 +4397,10 @@
       <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="2" cm="1">
+      <c r="D20" s="21" cm="1">
         <f t="array" ref="D20">_xlfn.SWITCH(C20,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4379,10 +4412,10 @@
       <c r="B21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="2" cm="1">
+      <c r="D21" s="21" cm="1">
         <f t="array" ref="D21">_xlfn.SWITCH(C21,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4394,12 +4427,12 @@
       <c r="B22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="2" cm="1">
+      <c r="C22" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="21" cm="1">
         <f t="array" ref="D22">_xlfn.SWITCH(C22,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4409,12 +4442,12 @@
       <c r="B23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="2" cm="1">
+      <c r="C23" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="21" cm="1">
         <f t="array" ref="D23">_xlfn.SWITCH(C23,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4424,12 +4457,12 @@
       <c r="B24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="2" cm="1">
+      <c r="C24" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="21" cm="1">
         <f t="array" ref="D24">_xlfn.SWITCH(C24,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4439,12 +4472,12 @@
       <c r="B25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="2" cm="1">
+      <c r="C25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="21" cm="1">
         <f t="array" ref="D25">_xlfn.SWITCH(C25,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4454,12 +4487,12 @@
       <c r="B26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="2" cm="1">
+      <c r="C26" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="21" cm="1">
         <f t="array" ref="D26">_xlfn.SWITCH(C26,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4469,12 +4502,12 @@
       <c r="B27" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="2" cm="1">
+      <c r="C27" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="21" cm="1">
         <f t="array" ref="D27">_xlfn.SWITCH(C27,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4484,10 +4517,10 @@
       <c r="B28" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="2" cm="1">
+      <c r="D28" s="21" cm="1">
         <f t="array" ref="D28">_xlfn.SWITCH(C28,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4499,10 +4532,10 @@
       <c r="B29" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="2" cm="1">
+      <c r="D29" s="21" cm="1">
         <f t="array" ref="D29">_xlfn.SWITCH(C29,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4514,12 +4547,12 @@
       <c r="B30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="2" cm="1">
+      <c r="C30" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="21" cm="1">
         <f t="array" ref="D30">_xlfn.SWITCH(C30,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4529,12 +4562,12 @@
       <c r="B31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2" cm="1">
+      <c r="C31" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="21" cm="1">
         <f t="array" ref="D31">_xlfn.SWITCH(C31,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4544,12 +4577,12 @@
       <c r="B32" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="2" cm="1">
+      <c r="C32" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="21" cm="1">
         <f t="array" ref="D32">_xlfn.SWITCH(C32,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4559,12 +4592,12 @@
       <c r="B33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="2" cm="1">
+      <c r="C33" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="21" cm="1">
         <f t="array" ref="D33">_xlfn.SWITCH(C33,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4574,12 +4607,12 @@
       <c r="B34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="2" cm="1">
+      <c r="C34" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="21" cm="1">
         <f t="array" ref="D34">_xlfn.SWITCH(C34,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4589,12 +4622,12 @@
       <c r="B35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="2" cm="1">
+      <c r="C35" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="21" cm="1">
         <f t="array" ref="D35">_xlfn.SWITCH(C35,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4604,12 +4637,12 @@
       <c r="B36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="2" cm="1">
+      <c r="C36" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="21" cm="1">
         <f t="array" ref="D36">_xlfn.SWITCH(C36,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4619,27 +4652,27 @@
       <c r="B37" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="2" cm="1">
+      <c r="D37" s="21" cm="1">
         <f t="array" ref="D37">_xlfn.SWITCH(C37,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>55</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="2" cm="1">
+      <c r="C38" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="21" cm="1">
         <f t="array" ref="D38">_xlfn.SWITCH(C38,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4649,12 +4682,12 @@
       <c r="B39" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="2" cm="1">
+      <c r="C39" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="21" cm="1">
         <f t="array" ref="D39">_xlfn.SWITCH(C39,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4664,12 +4697,12 @@
       <c r="B40" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="2" cm="1">
+      <c r="C40" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="21" cm="1">
         <f t="array" ref="D40">_xlfn.SWITCH(C40,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4679,12 +4712,12 @@
       <c r="B41" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2" cm="1">
+      <c r="C41" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="21" cm="1">
         <f t="array" ref="D41">_xlfn.SWITCH(C41,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4694,12 +4727,12 @@
       <c r="B42" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="2" cm="1">
+      <c r="C42" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="21" cm="1">
         <f t="array" ref="D42">_xlfn.SWITCH(C42,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4709,10 +4742,10 @@
       <c r="B43" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="2" cm="1">
+      <c r="D43" s="21" cm="1">
         <f t="array" ref="D43">_xlfn.SWITCH(C43,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4724,10 +4757,10 @@
       <c r="B44" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="2" cm="1">
+      <c r="D44" s="21" cm="1">
         <f t="array" ref="D44">_xlfn.SWITCH(C44,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4739,12 +4772,12 @@
       <c r="B45" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="2" cm="1">
+      <c r="C45" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="21" cm="1">
         <f t="array" ref="D45">_xlfn.SWITCH(C45,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4754,12 +4787,12 @@
       <c r="B46" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2" cm="1">
+      <c r="C46" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="21" cm="1">
         <f t="array" ref="D46">_xlfn.SWITCH(C46,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4769,12 +4802,12 @@
       <c r="B47" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="2" cm="1">
+      <c r="C47" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="21" cm="1">
         <f t="array" ref="D47">_xlfn.SWITCH(C47,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="96.6" customHeight="1" x14ac:dyDescent="0.35">
@@ -4784,12 +4817,12 @@
       <c r="B48" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="2" cm="1">
+      <c r="C48" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="21" cm="1">
         <f t="array" ref="D48">_xlfn.SWITCH(C48,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4799,10 +4832,10 @@
       <c r="B49" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D49" s="2" cm="1">
+      <c r="D49" s="21" cm="1">
         <f t="array" ref="D49">_xlfn.SWITCH(C49,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4814,12 +4847,12 @@
       <c r="B50" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="2" cm="1">
+      <c r="C50" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="21" cm="1">
         <f t="array" ref="D50">_xlfn.SWITCH(C50,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="99.6" customHeight="1" x14ac:dyDescent="0.35">
@@ -4829,12 +4862,12 @@
       <c r="B51" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2" cm="1">
+      <c r="C51" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="21" cm="1">
         <f t="array" ref="D51">_xlfn.SWITCH(C51,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="97.2" customHeight="1" x14ac:dyDescent="0.35">
@@ -4844,12 +4877,12 @@
       <c r="B52" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="2" cm="1">
+      <c r="C52" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="21" cm="1">
         <f t="array" ref="D52">_xlfn.SWITCH(C52,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4859,12 +4892,12 @@
       <c r="B53" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="2" cm="1">
+      <c r="C53" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="21" cm="1">
         <f t="array" ref="D53">_xlfn.SWITCH(C53,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4874,12 +4907,12 @@
       <c r="B54" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2" cm="1">
+      <c r="C54" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="21" cm="1">
         <f t="array" ref="D54">_xlfn.SWITCH(C54,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4889,12 +4922,12 @@
       <c r="B55" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="2" cm="1">
+      <c r="C55" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="21" cm="1">
         <f t="array" ref="D55">_xlfn.SWITCH(C55,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="109.8" x14ac:dyDescent="0.35">
@@ -4904,10 +4937,10 @@
       <c r="B56" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D56" s="2" cm="1">
+      <c r="D56" s="21" cm="1">
         <f t="array" ref="D56">_xlfn.SWITCH(C56,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>1</v>
       </c>
@@ -4919,10 +4952,10 @@
       <c r="B57" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="2" cm="1">
+      <c r="D57" s="21" cm="1">
         <f t="array" ref="D57">_xlfn.SWITCH(C57,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -4934,12 +4967,12 @@
       <c r="B58" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" s="2" cm="1">
+      <c r="C58" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="21" cm="1">
         <f t="array" ref="D58">_xlfn.SWITCH(C58,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4949,10 +4982,10 @@
       <c r="B59" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="2" cm="1">
+      <c r="D59" s="21" cm="1">
         <f t="array" ref="D59">_xlfn.SWITCH(C59,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -4964,12 +4997,12 @@
       <c r="B60" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" s="2" cm="1">
+      <c r="C60" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="21" cm="1">
         <f t="array" ref="D60">_xlfn.SWITCH(C60,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4979,12 +5012,12 @@
       <c r="B61" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="2" cm="1">
+      <c r="C61" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="21" cm="1">
         <f t="array" ref="D61">_xlfn.SWITCH(C61,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -4994,12 +5027,12 @@
       <c r="B62" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" cm="1">
+      <c r="C62" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="21" cm="1">
         <f t="array" ref="D62">_xlfn.SWITCH(C62,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5009,12 +5042,12 @@
       <c r="B63" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" cm="1">
+      <c r="C63" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="21" cm="1">
         <f t="array" ref="D63">_xlfn.SWITCH(C63,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5024,12 +5057,12 @@
       <c r="B64" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="2" cm="1">
+      <c r="C64" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="21" cm="1">
         <f t="array" ref="D64">_xlfn.SWITCH(C64,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5039,12 +5072,12 @@
       <c r="B65" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" s="2" cm="1">
+      <c r="C65" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="21" cm="1">
         <f t="array" ref="D65">_xlfn.SWITCH(C65,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5054,10 +5087,10 @@
       <c r="B66" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D66" s="2" cm="1">
+      <c r="D66" s="21" cm="1">
         <f t="array" ref="D66">_xlfn.SWITCH(C66,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -5069,12 +5102,12 @@
       <c r="B67" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" s="2" cm="1">
+      <c r="C67" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="21" cm="1">
         <f t="array" ref="D67">_xlfn.SWITCH(C67,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5084,12 +5117,12 @@
       <c r="B68" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="2" cm="1">
+      <c r="C68" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="21" cm="1">
         <f t="array" ref="D68">_xlfn.SWITCH(C68,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5099,12 +5132,12 @@
       <c r="B69" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" cm="1">
+      <c r="C69" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="21" cm="1">
         <f t="array" ref="D69">_xlfn.SWITCH(C69,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5114,12 +5147,12 @@
       <c r="B70" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" cm="1">
+      <c r="C70" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="21" cm="1">
         <f t="array" ref="D70">_xlfn.SWITCH(C70,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5129,12 +5162,12 @@
       <c r="B71" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="2" cm="1">
+      <c r="C71" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="21" cm="1">
         <f t="array" ref="D71">_xlfn.SWITCH(C71,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5144,12 +5177,12 @@
       <c r="B72" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D72" s="2" cm="1">
+      <c r="C72" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="21" cm="1">
         <f t="array" ref="D72">_xlfn.SWITCH(C72,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5159,10 +5192,10 @@
       <c r="B73" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D73" s="2" cm="1">
+      <c r="D73" s="21" cm="1">
         <f t="array" ref="D73">_xlfn.SWITCH(C73,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.25</v>
       </c>
@@ -5174,12 +5207,12 @@
       <c r="B74" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" s="2" cm="1">
+      <c r="C74" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="21" cm="1">
         <f t="array" ref="D74">_xlfn.SWITCH(C74,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="94.2" x14ac:dyDescent="0.35">
@@ -5189,10 +5222,10 @@
       <c r="B75" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D75" s="2" cm="1">
+      <c r="D75" s="21" cm="1">
         <f t="array" ref="D75">_xlfn.SWITCH(C75,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
         <v>0.75</v>
       </c>
@@ -5204,18 +5237,24 @@
       <c r="B76" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" cm="1">
+      <c r="C76" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="21" cm="1">
         <f t="array" ref="D76">_xlfn.SWITCH(C76,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</f>
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="25" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C79" s="2"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="GMgWDi/6+wKmu1QZ5rZKPdtdDCNM7wbWTIbCKl1tjWeTFyXdMeypDpGfFXJVjonE0zZNfFm5GEoQPvde07Io9w==" saltValue="SCSgi04tkLA1F+XXLJ1t9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations xWindow="1284" yWindow="779" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Organization Response" prompt="Select 1 out of A,B,C,D" sqref="C2:C76" xr:uid="{38769ACA-BE52-4C22-A94E-0EFE0281E8FE}">
       <formula1>"A,B,C,D"</formula1>
@@ -5230,7 +5269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6992F667-9237-424C-9FAB-1605BDA91A9B}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -5258,278 +5297,278 @@
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A2, User_Responses!$D$2:$D$76)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C2" s="16">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14">
         <v>3</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="23">
         <f>B2*C2</f>
-        <v>2.0999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A3, User_Responses!$D$2:$D$76)</f>
-        <v>0.5</v>
-      </c>
-      <c r="C3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14">
         <v>3</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="23">
         <f t="shared" ref="D3:D17" si="0">B3*C3</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A4, User_Responses!$D$2:$D$76)</f>
-        <v>0.625</v>
-      </c>
-      <c r="C4" s="16">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14">
         <v>3</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="23">
         <f t="shared" si="0"/>
-        <v>1.875</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A5, User_Responses!$D$2:$D$76)</f>
-        <v>0.8125</v>
-      </c>
-      <c r="C5" s="16">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14">
         <v>2</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="23">
         <f t="shared" si="0"/>
-        <v>1.625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A6, User_Responses!$D$2:$D$76)</f>
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="C6" s="16">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14">
         <v>2</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="23">
         <f t="shared" si="0"/>
-        <v>1.4166666666666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A7, User_Responses!$D$2:$D$76)</f>
-        <v>0.375</v>
-      </c>
-      <c r="C7" s="16">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14">
         <v>3</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="23">
         <f t="shared" si="0"/>
-        <v>1.125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A8, User_Responses!$D$2:$D$76)</f>
-        <v>0.85</v>
-      </c>
-      <c r="C8" s="16">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14">
         <v>2</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="23">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A9, User_Responses!$D$2:$D$76)</f>
-        <v>0.45</v>
-      </c>
-      <c r="C9" s="16">
-        <v>1</v>
-      </c>
-      <c r="D9" s="17">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14">
+        <v>1</v>
+      </c>
+      <c r="D9" s="23">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A10, User_Responses!$D$2:$D$76)</f>
-        <v>0.6</v>
-      </c>
-      <c r="C10" s="16">
+        <v>1</v>
+      </c>
+      <c r="C10" s="14">
         <v>2</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="23">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A11, User_Responses!$D$2:$D$76)</f>
-        <v>0.8</v>
-      </c>
-      <c r="C11" s="16">
+        <v>1</v>
+      </c>
+      <c r="C11" s="14">
         <v>2</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="23">
         <f t="shared" si="0"/>
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A12, User_Responses!$D$2:$D$76)</f>
-        <v>0.65</v>
-      </c>
-      <c r="C12" s="16">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14">
         <v>2</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="23">
         <f t="shared" si="0"/>
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A13, User_Responses!$D$2:$D$76)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C13" s="16">
-        <v>1</v>
-      </c>
-      <c r="D13" s="17">
+        <v>0.85</v>
+      </c>
+      <c r="C13" s="14">
+        <v>1</v>
+      </c>
+      <c r="D13" s="23">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A14, User_Responses!$D$2:$D$76)</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C14" s="16">
+        <v>0.35</v>
+      </c>
+      <c r="C14" s="14">
         <v>2</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="23">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A15, User_Responses!$D$2:$D$76)</f>
-        <v>0.7</v>
-      </c>
-      <c r="C15" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="C15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="23">
         <f t="shared" si="0"/>
-        <v>2.0999999999999996</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A16, User_Responses!$D$2:$D$76)</f>
-        <v>0.8</v>
-      </c>
-      <c r="C16" s="16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="23">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="22">
         <f>AVERAGEIF(User_Responses!$A$2:$A$76, A17, User_Responses!$D$2:$D$76)</f>
-        <v>0.6</v>
-      </c>
-      <c r="C17" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="C17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="23">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="24">
         <f>SUM(D2:D17)/SUM(C2:C17)</f>
-        <v>0.63651960784313721</v>
+        <v>0.83382352941176474</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="7" t="str">
+      <c r="C21" s="28" t="str">
         <f>IF(C19&lt;=40%, "🟢 Cloud Optimized State", IF(C19&lt;=60%, "🟡 Cloud Resilient State", IF(C19&lt;=80%, "🟠 Elevated Cloud Exposure", "🔴 Critical Cloud Threat Posture")))</f>
-        <v>🟠 Elevated Cloud Exposure</v>
+        <v>🔴 Critical Cloud Threat Posture</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="15" t="s">
         <v>104</v>
       </c>
       <c r="C23" t="s">
@@ -5540,194 +5579,200 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="17">
         <v>2</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="18">
         <v>1.3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="20">
-        <v>1</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="C25" s="17">
+        <v>1</v>
+      </c>
+      <c r="D25" s="18">
         <v>0.45</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="17">
         <v>3</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="18">
         <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="17">
         <v>2</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="18">
         <v>1.625</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="17">
         <v>2</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="18">
         <v>1.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="17">
         <v>2</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="18">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="20">
-        <v>1</v>
-      </c>
-      <c r="D30" s="21">
+      <c r="C30" s="17">
+        <v>1</v>
+      </c>
+      <c r="D30" s="18">
         <v>0.8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="17">
         <v>2</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="18">
         <v>1.4166666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="17">
         <v>2</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32" s="18">
         <v>1.2</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="19" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="17">
         <v>3</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="18">
         <v>2.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="19" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="20">
-        <v>1</v>
-      </c>
-      <c r="D34" s="21">
+      <c r="C34" s="17">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="19" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="17">
         <v>3</v>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="18">
         <v>2.0999999999999996</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="19" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="17">
         <v>3</v>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="18">
         <v>1.875</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="19" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="17">
         <v>3</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D37" s="18">
         <v>1.125</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="19" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="17">
         <v>2</v>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="18">
         <v>1.6</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="19" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="17">
         <v>2</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="18">
         <v>1.7</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="19" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="17">
         <v>34</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="18">
         <v>21.641666666666669</v>
       </c>
     </row>
+    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
+  <sheetProtection algorithmName="SHA-512" hashValue="R2WI8CEmDpeRewfds2MwGTjYI5AZUbWxc2erI3ppR8Kv0dKdKlWzVrPhd18F0TJWmKT+XzQqbHfbb5ZV+z36vA==" saltValue="WPW/Eqp0LyDLmyGHGNNW2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Select Weight" prompt="Select 1 from (1,2,3,4)" sqref="C2:C17" xr:uid="{C7585D9D-7E7D-4094-AB10-9345EED1BEEF}">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
@@ -5742,7 +5787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C40AB3C-9D76-48CC-B399-D4A50D69AD7B}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="91.21875" customWidth="1"/>
@@ -5751,13 +5796,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="20" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5765,10 +5810,10 @@
       <c r="A2" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5776,10 +5821,10 @@
       <c r="A3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>115</v>
       </c>
     </row>
@@ -5787,10 +5832,10 @@
       <c r="A4" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5798,14 +5843,20 @@
       <c r="A5" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>121</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="l9d6383FJymYN7pG9Szg5tvq/SjMuGSN4jbjoJoIN3WMIN8e2CQgJs1r6g6tPGNw1CvuyzQYERH5XAZSRGu6MA==" saltValue="Tq2Qh2eBKwLKIglf5Z0LcA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
